--- a/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
+++ b/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:BT9"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="33" min="1" max="71"/>
@@ -3305,6 +3305,204 @@
       <c r="BM9" s="49" t="inlineStr">
         <is>
           <t>SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-29_SPX_real_007</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>Apertura 9:30 ET (call side); put side diferido unos minutos hasta definicion del mercado</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>Intraday 0DTE</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>Screenshots QuantData + order book SPX (sesion Eolo Crop LLM 04-jun)</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>month_end_real_trade_LIVE</t>
+        </is>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>IV apertura 16% (QuantData); rango operativo esperado 14-17%</t>
+        </is>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>ARV ~5% estable al inicio; ARV subiendo luego con caida de SPX</t>
+        </is>
+      </c>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>Mercado alcista en apertura</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>Cierre de mes (ultimo trading day de mayo)</t>
+        </is>
+      </c>
+      <c r="M10" s="33" t="inlineStr">
+        <is>
+          <t>Month-end rebalancing</t>
+        </is>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>MVC muy fuerte en 7600 calls (resistencia); gamma cero en 7550-7555</t>
+        </is>
+      </c>
+      <c r="P10" s="33" t="inlineStr">
+        <is>
+          <t>Cierre de mes; sin fuerza vendedora visible</t>
+        </is>
+      </c>
+      <c r="Q10" s="33" t="inlineStr">
+        <is>
+          <t>Alcista en apertura con fuerte resistencia 7600 calls</t>
+        </is>
+      </c>
+      <c r="AH10" s="33" t="inlineStr">
+        <is>
+          <t>MVC 7600 (resistencia calls); gamma cero 7550-7555</t>
+        </is>
+      </c>
+      <c r="AI10" s="33" t="inlineStr">
+        <is>
+          <t>quantdata</t>
+        </is>
+      </c>
+      <c r="AJ10" s="33" t="inlineStr">
+        <is>
+          <t>N/A (trade discrecional de Juan, pre-CROP en SPX)</t>
+        </is>
+      </c>
+      <c r="AT10" s="33" t="inlineStr">
+        <is>
+          <t>IRON_CONDOR: call spread short 7625 + put spread short 7555 / long 7550</t>
+        </is>
+      </c>
+      <c r="AU10" s="33" t="inlineStr">
+        <is>
+          <t>Call 7625 = MVC 7600 + $25 (regla minimo +$10, ampliado por cierre de mes). Put 7555 coincidente con gamma cero.</t>
+        </is>
+      </c>
+      <c r="AW10" s="33" t="inlineStr">
+        <is>
+          <t>0DTE</t>
+        </is>
+      </c>
+      <c r="AX10" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" s="33" t="inlineStr">
+        <is>
+          <t>N/A (trade solo-Juan)</t>
+        </is>
+      </c>
+      <c r="AZ10" s="33" t="inlineStr">
+        <is>
+          <t>IV 16% dentro de rango 14-17% = SPX en rango. ARV ~5% con MVC fuerte. Sin fuerza bajista -&gt; espero gamma cero definido para put side.</t>
+        </is>
+      </c>
+      <c r="BB10" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-073 (cushion MVC call side), TR-Juan-074 (put en gamma cero), TR-Juan-075 (IV gate 14-17%), TR-Juan-076 (cierre de mes), TR-Juan-040 (entry window)</t>
+        </is>
+      </c>
+      <c r="BC10" s="33" t="inlineStr">
+        <is>
+          <t>CASO REAL ejecutado y documentado por Juan. SPX es REFERENCIA: conversion percentual a tickers CROP (SPY/QQQ/IWM/TQQQ). Origen de reglas TR-Juan-073/074/075/076.</t>
+        </is>
+      </c>
+      <c r="BD10" s="33" t="inlineStr">
+        <is>
+          <t>SI (real, cuenta Juan)</t>
+        </is>
+      </c>
+      <c r="BE10" s="33" t="inlineStr">
+        <is>
+          <t>Credit ambas puntas (call spread 7625 + put spread 7555/7550)</t>
+        </is>
+      </c>
+      <c r="BF10" s="33" t="inlineStr">
+        <is>
+          <t>Cierre anticipado mismo dia</t>
+        </is>
+      </c>
+      <c r="BG10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="33" t="inlineStr">
+        <is>
+          <t>WIN ambas puntas (monto exacto no informado)</t>
+        </is>
+      </c>
+      <c r="BI10" s="33" t="inlineStr">
+        <is>
+          <t>Cierre anticipado: theta importante ya capturado, no esperar expiracion</t>
+        </is>
+      </c>
+      <c r="BJ10" s="33" t="inlineStr">
+        <is>
+          <t>Cushion call &gt;= $10 sobre MVC (SPX). Put en gamma cero como recomendacion. IV 14-17% + ARV estable = rango vendible. Tomar ganancia de theta sin esperar expiry.</t>
+        </is>
+      </c>
+      <c r="BK10" s="33" t="inlineStr">
+        <is>
+          <t>{"setup_type": "iron_condor_mvc_gammazero", "iv_open_pct": 16, "arv_pct": 5, "mvc_strike": 7600, "short_call": 7625, "short_put": 7555, "long_put": 7550, "gamma_zero_zone": [7550, 7555], "dte": 0, "month_end": true, "outcome": "win_both_sides_closed_early"}</t>
+        </is>
+      </c>
+      <c r="BL10" s="33" t="inlineStr">
+        <is>
+          <t>spx;iron_condor;0dte;month_end;mvc_cushion;gamma_zero;iv_gate;arv;real_trade;win;theta_capture;29may2026</t>
+        </is>
+      </c>
+      <c r="BM10" s="33" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="BN10" s="33" t="inlineStr">
+        <is>
+          <t>theta_harvest_iron_condor</t>
+        </is>
+      </c>
+      <c r="BO10" s="33" t="inlineStr">
+        <is>
+          <t>Controlado: strikes fuera de MVC y sobre gamma cero</t>
+        </is>
+      </c>
+      <c r="BP10" s="33" t="inlineStr">
+        <is>
+          <t>Intraday — cierre anticipado al capturar theta</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -4739,12 +4937,12 @@
       </c>
       <c r="B16" s="48" t="inlineStr">
         <is>
-          <t>Volume spike premarket + gap apertura fuerte</t>
+          <t>CUSHION_TIERED_PER_DTE — sizing/cushion check pre-entry</t>
         </is>
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
-          <t>Esperar señal exhaustion primeros 30min</t>
+          <t>Cushion mínimo per DTE: 0DTE absoluto (SPX $10, SPY $1, QQQ $0.50, IWM $0.30); DTE 1-4 &gt;=0.30% del spot; VIX EXPANDING o evento próximo: doblar cushion. Sprint INTRADAY-THETA-PIVOT 2026-06-04: override TR-Juan-001 original 1% rule que era ~8x conservadora vs práctica real.</t>
         </is>
       </c>
       <c r="D16" s="48" t="inlineStr">
@@ -4769,7 +4967,7 @@
       </c>
       <c r="H16" s="52" t="inlineStr">
         <is>
-          <t>TACTICAL</t>
+          <t>AXIOMA</t>
         </is>
       </c>
     </row>
@@ -7086,40 +7284,208 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="33" t="inlineStr">
         <is>
           <t>TR-Juan-072</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="33" t="inlineStr">
         <is>
           <t>INTRADAY_THETA_AXIOM — cualquier proposal/decisión</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="33" t="inlineStr">
         <is>
           <t>CROP es theta harvest INTRADAY puro. DTE 0-4 estricto. Entry 9:30-15:30 ET. NO overnight. Strategy #1: vender premium theta extremo. Strategy #2: close 50-60% capture cuando theta+price erosionan premium. Sprint INTRADAY-THETA-PIVOT 2026-06-04 overrides Master Plan v2.1 sec 7.1 que decía 30-45 DTE.</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="33" t="inlineStr">
         <is>
           <t>MAXIMA</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
+      <c r="E73" s="33" t="inlineStr"/>
+      <c r="F73" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="33" t="inlineStr">
         <is>
           <t>Filosofía operativa core CROP — confirmada por Juan 2026-06-04. Reemplaza la guidance v2.1 30-45 DTE long-gamma. Validated en sesión live.</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="33" t="inlineStr">
         <is>
           <t>AXIOMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-073</t>
+        </is>
+      </c>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>Call side strike selection (SELL_CALL / call wing de IC) con MVC (max volume call strike) identificado en QuantData</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="inlineStr">
+        <is>
+          <t>Short call minimo $10 arriba del MVC en SPX (referencia Juan). Conversion percentual (~0.13% del spot) a tickers CROP: SPY &gt;= $1, QQQ &gt;= $0.70, IWM/TQQQ &gt;= 0.13% del spot. Criterio LAXO: minimo orientativo aprobado por Juan, no rechazar proposals por margen apenas inferior. En cierre de mes Juan amplia el cushion (29-may uso +$25 sobre MVC).</t>
+        </is>
+      </c>
+      <c r="D74" s="33" t="inlineStr">
+        <is>
+          <t>MAXIMA</t>
+        </is>
+      </c>
+      <c r="E74" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-29_SPX_real_007</t>
+        </is>
+      </c>
+      <c r="F74" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G74" s="33" t="inlineStr">
+        <is>
+          <t>Origen: trade real Juan 29-may-2026 SPX. SPX es referencia; conversion a tickers que opera CROP. Aprobado por Juan 04-jun-2026 (respuestas 1-2-4).</t>
+        </is>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>PROTOCOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-074</t>
+        </is>
+      </c>
+      <c r="B75" s="33" t="inlineStr">
+        <is>
+          <t>Put side strike selection con gamma_zero_strike disponible en QuantData</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="inlineStr">
+        <is>
+          <t>RECOMENDACION (no gate duro): preferir short put coincidente con gamma_zero_strike +/- 1 strike. No usar magnet/MVC para el put side. Desviacion permitida si otro strike puntua mejor en scoring 7.5 (OI, credit). Si gamma cero ambiguo (gamma ~0 en zona amplia), esperar definicion del mercado antes de entrar (Juan 29-may espero unos minutos).</t>
+        </is>
+      </c>
+      <c r="D75" s="33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E75" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-29_SPX_real_007</t>
+        </is>
+      </c>
+      <c r="F75" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G75" s="33" t="inlineStr">
+        <is>
+          <t>Juan confirmo 04-jun-2026 (respuesta 3): es una recomendacion, NO regla dura.</t>
+        </is>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>TACTICAL_PLUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-075</t>
+        </is>
+      </c>
+      <c r="B76" s="33" t="inlineStr">
+        <is>
+          <t>IV (QuantData) en rango [14%, 17%] con ARV estable (~5%)</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>Regimen de rango: SPX/SPY dificilmente supere strikes bien ubicados -&gt; favorable para vender premium en ambas puntas. Seguir IV y ARV a lo largo del dia: si ARV diverge al alza mientras el subyacente cae = momentum bajista incipiente -&gt; NO abrir mas puts. Cambios en IV/ARV son senial significativa.</t>
+        </is>
+      </c>
+      <c r="D76" s="33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E76" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-29_SPX_real_007</t>
+        </is>
+      </c>
+      <c r="F76" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G76" s="33" t="inlineStr">
+        <is>
+          <t>IV gate operativo de Juan. Aprobado 04-jun-2026 (respuesta 1).</t>
+        </is>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>TACTICAL_PLUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-076</t>
+        </is>
+      </c>
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>Sesion de cierre de mes (ultimo trading day del mes)</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="inlineStr">
+        <is>
+          <t>Positioning institucional especial, magnet effect mas fuerte. Considerar reducir size o ampliar cushion call side (Juan 29-may: +$25 sobre MVC vs minimo $10). Esperar confirmacion/definicion del mercado antes del put side.</t>
+        </is>
+      </c>
+      <c r="D77" s="33" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E77" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-29_SPX_real_007</t>
+        </is>
+      </c>
+      <c r="F77" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G77" s="33" t="inlineStr">
+        <is>
+          <t>Aprobado por Juan 04-jun-2026 (respuesta 1).</t>
+        </is>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>TACTICAL</t>
         </is>
       </c>
     </row>

--- a/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
+++ b/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BT11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="33" min="1" max="71"/>
@@ -3503,6 +3503,73 @@
       <c r="BP10" s="33" t="inlineStr">
         <is>
           <t>Intraday — cierre anticipado al capturar theta</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01_SPX_real_008</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Apertura 9:30 + scaling intraday hasta ~12:48 ET</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>Intraday 0DTE multi-leg</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Sesion Eolo Crop LLM (Juan trade live)</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>monday_post_eom_LIVE</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>IV 16-17% subiendo intraday (ARV abrió alto)</t>
+        </is>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>MVC=7590 calls (resistencia fuerte); GEX en 7600 (fuga y bajada); gamma_zero ~7540-7545</t>
+        </is>
+      </c>
+      <c r="Q11" s="33" t="inlineStr">
+        <is>
+          <t>IC simetrico inicial + scaling put side en dip intraday</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>WIN. Put side: 100% capture (precio se alejó, dejó expirar). Call side: recompra breakeven ~12:48 ET cuando RSI doble cruce + higher highs/lows confirmaron bullish reversal. Pattern emergente: IC simétrico inicial + scaling PUT side en dip intraday. Exit signal call side: RSI doble cruce + price action contraria a posición. Validates TR-Juan-072 (intraday only) + TR-Juan-077 (OR breakout).</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>GOLD</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -7486,6 +7553,44 @@
       <c r="H77" s="33" t="inlineStr">
         <is>
           <t>TACTICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-077</t>
+        </is>
+      </c>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>OPENING_RANGE_GATE — usar OR state para guiar selección</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="inlineStr">
+        <is>
+          <t>Opening Range = high/low primeros 6 min (9:30-9:36 ET). Niveles: ORH, ORL, OR_mid. Fibonacci ext arriba/abajo (1.618, 2.236, 2.618). Si precio en [ORL, ORH] durante mañana → range trading → IC simétrico favorable. Si rompe ORH con MACD+RSI confirm → bullish breakout, escalar PUT side en dips back. Si rompe ORL → bearish, escalar CALL side en bounces. Targets: 3-4x ATR(14).</t>
+        </is>
+      </c>
+      <c r="D78" s="33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E78" s="33" t="inlineStr"/>
+      <c r="F78" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G78" s="33" t="inlineStr">
+        <is>
+          <t>Basado en código TOS de Juan 2026-06-04. Wire via backtest/opening_range.py + MarketSnapshot or_* fields.</t>
+        </is>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>TACTICAL_PLUS</t>
         </is>
       </c>
     </row>

--- a/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
+++ b/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
@@ -3557,17 +3557,17 @@
           <t>IC simetrico inicial + scaling put side en dip intraday</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BD11" s="33" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BJ11" s="33" t="inlineStr">
         <is>
           <t>WIN. Put side: 100% capture (precio se alejó, dejó expirar). Call side: recompra breakeven ~12:48 ET cuando RSI doble cruce + higher highs/lows confirmaron bullish reversal. Pattern emergente: IC simétrico inicial + scaling PUT side en dip intraday. Exit signal call side: RSI doble cruce + price action contraria a posición. Validates TR-Juan-072 (intraday only) + TR-Juan-077 (OR breakout).</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BM11" s="33" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B16" s="48" t="inlineStr">
         <is>
-          <t>CUSHION_TIERED_PER_DTE — sizing/cushion check pre-entry</t>
+          <t>CUSHION_TIERED_PER_DTE — sizing/cushion pre-entry para cualquier DTE 0-4</t>
         </is>
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
-          <t>Cushion mínimo per DTE: 0DTE absoluto (SPX $10, SPY $1, QQQ $0.50, IWM $0.30); DTE 1-4 &gt;=0.30% del spot; VIX EXPANDING o evento próximo: doblar cushion. Sprint INTRADAY-THETA-PIVOT 2026-06-04: override TR-Juan-001 original 1% rule que era ~8x conservadora vs práctica real.</t>
+          <t>0DTE PERMITIDO con cushion MÍNIMO absoluto: SPX &gt;=$10 arriba spot, SPY &gt;=$1, QQQ &gt;=$0.50, IWM &gt;=$0.30. DTE 1-4: cushion &gt;=0.30% del spot. VIX EXPANDING o evento próximo: doblar el cushion. Esta regla NO prohíbe 0DTE — define el cushion mínimo aceptable para entrar. Sprint INTRADAY-THETA-PIVOT 2026-06-04 reemplazó cushion percentual fijo.</t>
         </is>
       </c>
       <c r="D16" s="48" t="inlineStr">

--- a/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
+++ b/llm_engine_eolo/kb/EOLO_ThetaHarvest_v1.4.xlsx
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:BT11"/>
+  <dimension ref="A1:BT12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="33" min="1" max="71"/>
@@ -3571,6 +3571,114 @@
         <is>
           <t>GOLD</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-04_SPY_real_009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9:44 ET (entry temprana, primeros 14 min de sesion)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Intraday 0DTE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Live session Eolo Crop</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AM_open_bottom_detection_LIVE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>IV 10.40 pct (LOW), ARV 2.52 pct (MUY LOW)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Net GEX heat map: fuerte negativo $748 (-$200M) y $750 (-$328M) - soportes naturales. MVC apertura $754.50 + presion fuerte $757 = magnet upper. Net Drift Calls -$1.81M (premium drift bajista pero spot resistente)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dia calm, sin macro events imminentes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Vela acercandose al pivot minimo del Opening Range + GEX heat map confirmando compra fuerte en magnet upper $755</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>SELL_PUT (temprana en confluencia OR pivot + GEX magnet)</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bottom detection temprana: pattern de theta harvest core. Confluencia OR pivot minimo + GEX heat map muestra fuerte compra en $755 magnet. NO esperar RSI/MACD - early entry justificada.</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>TR-Juan-077 (OR levels); TR-Juan-078 (bottom detection at OR pivot); TR-Juan-079 (multi-indicator confluence)</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>SELL_PUT temprana - Strike y contratos: TBD (pending Juan input)</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>Pattern core theta harvest validado: detectar bottom intraday TEMPRANO (primeros 20-30 min) cuando hay confluencia (1) precio cerca OR pivot minimo + (2) GEX heat map confirma poder comprador en magnet upper. 'Aca esta la clave del theta Harvest. Ser inteligentes para entrar temprano siempre.'</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>SELL_PUT</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="BP12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -4355,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -7589,6 +7697,120 @@
         </is>
       </c>
       <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>TACTICAL_PLUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-078</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t>BOTTOM_DETECTION_AT_OR_PIVOT — vela cerca ORL pivot + GEX heat map fuerte compra magnet upper, primeros 20-30 min sesión</t>
+        </is>
+      </c>
+      <c r="C79" s="33" t="inlineStr">
+        <is>
+          <t>Vela acercándose al pivot mínimo del Opening Range (~ORL o cerca) + Net GEX heat map muestra fuerte poder comprador en strike upper (magnet) → señal de bottom intraday early. Oportunidad SELL_PUT temprana. NO esperar confirmación tardía RSI/MACD — la confluencia OR+GEX es suficiente. Aplica primeros 20-30 min de la sesión.</t>
+        </is>
+      </c>
+      <c r="D79" s="33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E79" s="33" t="inlineStr"/>
+      <c r="F79" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G79" s="33" t="inlineStr">
+        <is>
+          <t>Sprint BUNDLED 2026-06-04. Pattern core theta harvest validated en CASE-Juan-003.</t>
+        </is>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>TACTICAL_PLUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-079</t>
+        </is>
+      </c>
+      <c r="B80" s="33" t="inlineStr">
+        <is>
+          <t>MULTI_INDICATOR_CONFLUENCE — pre-entry check de 4 indicadores</t>
+        </is>
+      </c>
+      <c r="C80" s="33" t="inlineStr">
+        <is>
+          <t>Para evaluar entry verificar confluence de los 4 indicadores: (1) Opening Range levels (ORH, ORL, OR_mid, Fibonacci ext 1.618/2.236/2.618); (2) VWAP (posición precio relativo); (3) Net Gamma exposure Per 1pct Move (distribución y polaridad por strike); (4) NetGEX heat map (strike x tiempo, magnets y walls). Los 4 deben dar señal coherente antes de ENTRY. Si 3 de 4 confirman pero 1 contradice, REVISAR cushion y reducir tamaño 50pct.</t>
+        </is>
+      </c>
+      <c r="D80" s="33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E80" s="33" t="inlineStr"/>
+      <c r="F80" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G80" s="33" t="inlineStr">
+        <is>
+          <t>Sprint BUNDLED 2026-06-04. Protocolo decision matrix multi-fuente.</t>
+        </is>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>PROTOCOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>TR-Juan-080</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t>SCALING_ESCALONADO_VS_PUNTA — selección de modo de entrada según conviction</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="inlineStr">
+        <is>
+          <t>Modos de entrada: (a) ESCALONADO — entrada en múltiples niveles cuando hay dudas, e.g. parcial al primer setup, parcial al pullback, parcial al breakout. (b) PUNTA — entrada full size en strike máximo OTM (deepest punta puts o calls) cuando confluencia clara. Target operativo: 40 contratos/día agregado entre ambos lados, con risk/reward controlado por TR-Juan-001 cushion.</t>
+        </is>
+      </c>
+      <c r="D81" s="33" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E81" s="33" t="inlineStr"/>
+      <c r="F81" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G81" s="33" t="inlineStr">
+        <is>
+          <t>Sprint BUNDLED 2026-06-04. Sizing/entry mode strategy doc.</t>
+        </is>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
         <is>
           <t>TACTICAL_PLUS</t>
         </is>
